--- a/data/trans_dic/ProblemasDormirP33b-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,62</t>
+          <t>9,36; 14,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 21,4</t>
+          <t>14,8; 21,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 17,29</t>
+          <t>13,36; 17,05</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,03</t>
+          <t>4,22; 11,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 22,89</t>
+          <t>18,79; 23,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 16,46</t>
+          <t>9,48; 16,58</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,01</t>
+          <t>9,18; 14,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 17,14</t>
+          <t>6,24; 16,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 14,56</t>
+          <t>8,36; 14,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,59</t>
+          <t>14,32; 19,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,32; 24,92</t>
+          <t>17,81; 25,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 21,58</t>
+          <t>17,12; 21,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 13,47</t>
+          <t>9,41; 13,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,21; 20,49</t>
+          <t>15,14; 20,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,81</t>
+          <t>13,35; 16,81</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58829; 92930</t>
+          <t>59454; 91054</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107746; 155222</t>
+          <t>107332; 153978</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180586; 235224</t>
+          <t>181844; 232003</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53114; 143459</t>
+          <t>50283; 142705</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>180017; 219475</t>
+          <t>180099; 222633</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>199291; 354196</t>
+          <t>204001; 356637</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64464; 98733</t>
+          <t>64707; 101703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63088; 159968</t>
+          <t>58277; 157228</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131776; 238577</t>
+          <t>136995; 241677</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>133700; 181527</t>
+          <t>132688; 178329</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>200603; 272849</t>
+          <t>195053; 275354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>352369; 436300</t>
+          <t>346202; 434841</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>333670; 466160</t>
+          <t>325701; 467253</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>564511; 760768</t>
+          <t>562143; 762810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>966335; 1205571</t>
+          <t>957431; 1205638</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProblemasDormirP33b-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 14,33</t>
+          <t>9,35; 14,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 21,23</t>
+          <t>17,82; 22,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 17,05</t>
+          <t>14,5; 18,05</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 11,96</t>
+          <t>9,34; 13,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,79; 23,22</t>
+          <t>18,96; 23,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 16,58</t>
+          <t>14,72; 17,95</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 14,43</t>
+          <t>8,96; 13,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 16,85</t>
+          <t>14,56; 19,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,75</t>
+          <t>12,25; 15,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 19,24</t>
+          <t>14,88; 19,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,81; 25,15</t>
+          <t>21,78; 26,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,51</t>
+          <t>19,16; 22,49</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,51</t>
+          <t>11,83; 14,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,14; 20,55</t>
+          <t>19,75; 22,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 16,81</t>
+          <t>16,13; 17,82</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73850</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>134990</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208840</t>
+          <t>229576</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59454; 91054</t>
+          <t>64548; 102479</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107332; 153978</t>
+          <t>130817; 165441</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181844; 232003</t>
+          <t>206567; 257226</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>105723</t>
+          <t>118202</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>200836</t>
+          <t>225669</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306559</t>
+          <t>343871</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50283; 142705</t>
+          <t>97936; 142534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>180099; 222633</t>
+          <t>203148; 247463</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204001; 356637</t>
+          <t>312161; 380511</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81023</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>117834</t>
+          <t>135789</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198857</t>
+          <t>224973</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64707; 101703</t>
+          <t>71984; 110004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58277; 157228</t>
+          <t>118299; 156053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136995; 241677</t>
+          <t>197950; 253394</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>169716</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>243634</t>
+          <t>267847</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398752</t>
+          <t>437564</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132688; 178329</t>
+          <t>147343; 194431</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>195053; 275354</t>
+          <t>243721; 293680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>346202; 434841</t>
+          <t>404024; 474300</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>457867</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>697294</t>
+          <t>778116</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1113009</t>
+          <t>1235984</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>325701; 467253</t>
+          <t>417781; 501711</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>562143; 762810</t>
+          <t>738160; 822248</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>957431; 1205638</t>
+          <t>1172707; 1295263</t>
         </is>
       </c>
     </row>
